--- a/experiments/results/resnet34/CIFAR-100/ASH/adaptive/std/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-100/ASH/adaptive/std/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -813,6 +813,104 @@
       <c r="O9" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=80,react_th=None,scale_th=2.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>69.83</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>92.88</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>97.28</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=85,react_th=None,scale_th=3.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=80,react_th=None,scale_th=3.0,type=std</t>
         </is>
       </c>
     </row>
